--- a/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
+++ b/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -817,15 +817,15 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>DIP-14</t>
+          <t>25k multivuelta</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Zocalo DIP-14</t>
+          <t>Trimmer de ganancia por sitio de medicion</t>
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
@@ -838,15 +838,15 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>100p</t>
+          <t>DIP-14</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>cond. ceramico C0G</t>
+          <t>Zocalo DIP-14</t>
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
@@ -859,11 +859,11 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>1n</t>
+          <t>100p</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
@@ -880,11 +880,11 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>47p</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
@@ -901,15 +901,15 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>47p</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>cond. ceramico/electrolitico</t>
+          <t>cond. ceramico C0G</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
@@ -922,11 +922,11 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>10u</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
@@ -943,11 +943,11 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>10u</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
@@ -964,15 +964,15 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>cond. poliester (film)</t>
+          <t>cond. ceramico/electrolitico</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
@@ -985,15 +985,15 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>15n</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>cond. poliester o C0G</t>
+          <t>cond. poliester (film)</t>
         </is>
       </c>
       <c r="D26" s="4" t="n"/>
@@ -1006,7 +1006,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2.2n</t>
+          <t>15n</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -1027,7 +1027,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3.3n</t>
+          <t>2.2n</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -1048,7 +1048,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3.9n</t>
+          <t>3.3n</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -1069,15 +1069,15 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>1N4148</t>
+          <t>3.9n</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>diodo</t>
+          <t>cond. poliester o C0G</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
@@ -1090,15 +1090,15 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1N4148</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>resistencia</t>
+          <t>diodo</t>
         </is>
       </c>
       <c r="D31" s="4" t="n"/>
@@ -1111,11 +1111,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -1132,11 +1132,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>10M</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
@@ -1153,11 +1153,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>10M</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
@@ -1279,11 +1279,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>56k</t>
+          <t>4.7k</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
@@ -1300,11 +1300,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>620k</t>
+          <t>56k</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
@@ -1321,11 +1321,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>91k</t>
+          <t>620k</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
@@ -1340,13 +1340,34 @@
       <c r="F42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="D43" s="7" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>91k</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>resistencia</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="5">
+        <f>IF(D43="","",B43*D43)</f>
+        <v/>
+      </c>
+      <c r="F43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E43" s="8">
-        <f>SUM(E4:E42)</f>
+      <c r="E44" s="8">
+        <f>SUM(E4:E43)</f>
         <v/>
       </c>
     </row>

--- a/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
+++ b/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BoM compacta AFE sEMG AuraVox (4 canales, incluye repuesto). Detalle por modulo en BoM_AFE_AuraVox.xlsx</t>
+          <t>BoM compacta AFE sEMG AuraVox (3 canales, incluye repuesto). Detalle por modulo en BoM_AFE_AuraVox.xlsx</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>SOIC14 a DIP14</t>
+          <t>SOIC8 a DIP8</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Adaptador SOIC-14 a DIP-14</t>
+          <t>Adaptador SOIC-8 a DIP-8</t>
         </is>
       </c>
       <c r="D4" s="4" t="n"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Cable a Arduino A1..A4 del STM32N6570-DK</t>
+          <t>Cable a Arduino A1..A3 del STM32N6570-DK</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -691,15 +691,15 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCP6004-I/SL</t>
+          <t>TS922AIYDT</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Op-amp cuadruple MCP6004</t>
+          <t>Op-amp doble TS922 (rail-to-rail, 4 MHz)</t>
         </is>
       </c>
       <c r="D12" s="4" t="n"/>
@@ -817,15 +817,15 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>25k multivuelta</t>
+          <t>DIP-8</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Trimmer de ganancia por sitio de medicion</t>
+          <t>Zocalo DIP-8</t>
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
@@ -838,15 +838,15 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>DIP-14</t>
+          <t>100p</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Zocalo DIP-14</t>
+          <t>cond. ceramico C0G</t>
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
@@ -859,11 +859,11 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>100p</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
@@ -880,11 +880,11 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>1n</t>
+          <t>47p</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
@@ -901,15 +901,15 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>47p</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>cond. ceramico C0G</t>
+          <t>cond. ceramico/electrolitico</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
@@ -922,11 +922,11 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>10u</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
@@ -943,11 +943,11 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>10u</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
@@ -964,15 +964,15 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>cond. ceramico/electrolitico</t>
+          <t>cond. poliester (film)</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
@@ -985,15 +985,15 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>15n</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>cond. poliester (film)</t>
+          <t>cond. poliester o C0G</t>
         </is>
       </c>
       <c r="D26" s="4" t="n"/>
@@ -1006,11 +1006,11 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>15n</t>
+          <t>2.2n</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2.2n</t>
+          <t>68n</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
@@ -1048,15 +1048,15 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3.3n</t>
+          <t>1N4148</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>cond. poliester o C0G</t>
+          <t>diodo</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
@@ -1069,15 +1069,15 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3.9n</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>cond. poliester o C0G</t>
+          <t>resistencia</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
@@ -1090,15 +1090,15 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>1N4148</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>diodo</t>
+          <t>resistencia</t>
         </is>
       </c>
       <c r="D31" s="4" t="n"/>
@@ -1111,11 +1111,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10M</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -1132,11 +1132,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>110k</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
@@ -1153,11 +1153,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>10M</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
@@ -1174,11 +1174,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>110k</t>
+          <t>2.7k</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
@@ -1195,11 +1195,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>20k</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -1216,11 +1216,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2.7k</t>
+          <t>390k</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
@@ -1237,11 +1237,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>240k</t>
+          <t>3k</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>390k</t>
+          <t>56k</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
@@ -1279,11 +1279,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>620k</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
@@ -1300,11 +1300,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>56k</t>
+          <t>75k</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
@@ -1319,55 +1319,13 @@
       <c r="F41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>620k</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>resistencia</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="5">
-        <f>IF(D42="","",B42*D42)</f>
-        <v/>
-      </c>
-      <c r="F42" s="6" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>91k</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>resistencia</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="5">
-        <f>IF(D43="","",B43*D43)</f>
-        <v/>
-      </c>
-      <c r="F43" s="6" t="n"/>
-    </row>
-    <row r="44">
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E44" s="8">
-        <f>SUM(E4:E43)</f>
+      <c r="E42" s="8">
+        <f>SUM(E4:E41)</f>
         <v/>
       </c>
     </row>

--- a/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
+++ b/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -544,15 +544,15 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Alcohol isopropilico / gel</t>
+          <t>SOT23 a DIP</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Alcohol isopropilico / gel</t>
+          <t>Adaptador SOT-23-5 a DIP</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
@@ -565,15 +565,15 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>jumper Dupont</t>
+          <t>Alcohol isopropilico / gel</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Cable a Arduino A1..A3 del STM32N6570-DK</t>
+          <t>Alcohol isopropilico / gel</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
@@ -586,15 +586,15 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>broche 4 mm</t>
+          <t>jumper Dupont</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Cable con broche (snap) para electrodo</t>
+          <t>Cable 5 V y GND desde el DK</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
@@ -607,15 +607,15 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>24 AWG rigido</t>
+          <t>jumper Dupont</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Cable para puentes</t>
+          <t>Cable a Arduino A1..A3 del STM32N6570-DK</t>
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
@@ -628,15 +628,15 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>3M Red Dot 2228/2560</t>
+          <t>broche 4 mm a pin</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Electrodo Ag/AgCl con broche</t>
+          <t>Cable de electrodo con broche (snap) 4 mm, idealmente apantallado</t>
         </is>
       </c>
       <c r="D9" s="4" t="n"/>
@@ -649,15 +649,15 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>INA333 modulo MCU-333</t>
+          <t>24 AWG rigido</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>INA333 (modulo MCU-333)</t>
+          <t>Cable para puentes</t>
         </is>
       </c>
       <c r="D10" s="4" t="n"/>
@@ -670,15 +670,15 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>deslizante</t>
+          <t>jumper Dupont</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Interruptor</t>
+          <t>Cables Dupont para el microfono</t>
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
@@ -691,15 +691,15 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>TS922AIYDT</t>
+          <t>header 2.54 mm 1x8 + hembra</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Op-amp doble TS922 (rail-to-rail, 4 MHz)</t>
+          <t>Conector en la placa para los 7 cables</t>
         </is>
       </c>
       <c r="D12" s="4" t="n"/>
@@ -712,15 +712,15 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>10 x 15 cm</t>
+          <t>3M Red Dot 2228/2560</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Perfboard</t>
+          <t>Electrodo Ag/AgCl con broche</t>
         </is>
       </c>
       <c r="D13" s="4" t="n"/>
@@ -733,15 +733,15 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>INA333 modulo MCU-333</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Pilas AA</t>
+          <t>INA333 (modulo MCU-333)</t>
         </is>
       </c>
       <c r="D14" s="4" t="n"/>
@@ -754,15 +754,15 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>3xAA</t>
+          <t>INMP441</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Portapilas 3 x AA</t>
+          <t>Modulo microfono digital INMP441 (I2S)</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>
@@ -775,15 +775,15 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCP1700-3302E TO-92</t>
+          <t>TS922AIYDT</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Regulador LDO 3.3 V</t>
+          <t>Op-amp doble TS922AIYDT (Global 001-TS922)</t>
         </is>
       </c>
       <c r="D16" s="4" t="n"/>
@@ -796,15 +796,15 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2.54 mm</t>
+          <t>10 x 15 cm</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Tira de headers macho/hembra</t>
+          <t>Perfboard</t>
         </is>
       </c>
       <c r="D17" s="4" t="n"/>
@@ -817,15 +817,15 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>DIP-8</t>
+          <t>TLV75733PDBVR</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Zocalo DIP-8</t>
+          <t>Regulador LDO 3.3 V TLV75733PDBVR (Global 014-75733)</t>
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
@@ -838,15 +838,15 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>100p</t>
+          <t>2.54 mm</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>cond. ceramico C0G</t>
+          <t>Tira de headers macho/hembra</t>
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
@@ -859,15 +859,15 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>1n</t>
+          <t>DIP-8</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>cond. ceramico C0G</t>
+          <t>Zocalo DIP-8</t>
         </is>
       </c>
       <c r="D20" s="4" t="n"/>
@@ -880,11 +880,11 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>47p</t>
+          <t>100p</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
@@ -901,15 +901,15 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>cond. ceramico/electrolitico</t>
+          <t>cond. ceramico C0G</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
@@ -922,15 +922,15 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>10u</t>
+          <t>47p</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>cond. ceramico/electrolitico</t>
+          <t>cond. ceramico C0G</t>
         </is>
       </c>
       <c r="D23" s="4" t="n"/>
@@ -943,11 +943,11 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
@@ -964,15 +964,15 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>10u</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>cond. poliester (film)</t>
+          <t>cond. ceramico/electrolitico</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
@@ -985,15 +985,15 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>15n</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>cond. poliester o C0G</t>
+          <t>cond. ceramico/electrolitico</t>
         </is>
       </c>
       <c r="D26" s="4" t="n"/>
@@ -1006,15 +1006,15 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2.2n</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>cond. poliester o C0G</t>
+          <t>cond. poliester (film)</t>
         </is>
       </c>
       <c r="D27" s="4" t="n"/>
@@ -1027,7 +1027,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>68n</t>
+          <t>15n</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -1048,15 +1048,15 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>1N4148</t>
+          <t>2.2n</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>diodo</t>
+          <t>cond. poliester o C0G</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
@@ -1069,7 +1069,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>68n</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>resistencia</t>
+          <t>cond. poliester o C0G</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
@@ -1090,15 +1090,15 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>1N4148</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>resistencia</t>
+          <t>diodo</t>
         </is>
       </c>
       <c r="D31" s="4" t="n"/>
@@ -1111,11 +1111,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>10M</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -1132,11 +1132,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>110k</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
@@ -1153,11 +1153,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>10M</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
@@ -1174,11 +1174,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2.7k</t>
+          <t>110k</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
@@ -1195,11 +1195,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>20k</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -1216,11 +1216,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>390k</t>
+          <t>2.7k</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3k</t>
+          <t>20k</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
@@ -1258,11 +1258,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>56k</t>
+          <t>390k</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>620k</t>
+          <t>3k</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
@@ -1300,11 +1300,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>75k</t>
+          <t>56k</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
@@ -1319,13 +1319,55 @@
       <c r="F41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="D42" s="7" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>620k</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>resistencia</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="5">
+        <f>IF(D42="","",B42*D42)</f>
+        <v/>
+      </c>
+      <c r="F42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>75k</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>resistencia</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="5">
+        <f>IF(D43="","",B43*D43)</f>
+        <v/>
+      </c>
+      <c r="F43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E42" s="8">
-        <f>SUM(E4:E41)</f>
+      <c r="E44" s="8">
+        <f>SUM(E4:E43)</f>
         <v/>
       </c>
     </row>

--- a/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
+++ b/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>15n</t>
+          <t>150n</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -1048,7 +1048,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2.2n</t>
+          <t>15n</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -1069,7 +1069,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>68n</t>
+          <t>2.2n</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1216,11 +1216,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2.7k</t>
+          <t>2.2k</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>20k</t>
+          <t>2.4k</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
@@ -1258,11 +1258,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>390k</t>
+          <t>2.7k</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3k</t>
+          <t>300k</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
@@ -1300,11 +1300,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>56k</t>
+          <t>390k</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
@@ -1321,11 +1321,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>620k</t>
+          <t>56k</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>75k</t>
+          <t>620k</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">

--- a/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
+++ b/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
@@ -523,15 +523,15 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>SOIC8 a DIP8</t>
+          <t>SOP8/TSSOP8 a DIP8</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Adaptador SOIC-8 a DIP-8</t>
+          <t>Adaptador SOP8/TSSOP8 a DIP8 doble cara (SOIC-8 1.27 mm + MSOP/TSSOP-8 0.65 mm)</t>
         </is>
       </c>
       <c r="D4" s="4" t="n"/>

--- a/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
+++ b/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="81">
   <si>
     <t xml:space="preserve">BoM compacta AFE sEMG AuraVox (3 canales, incluye repuesto). Detalle por modulo en BoM_AFE_AuraVox.xlsx</t>
   </si>
@@ -175,6 +175,9 @@
     <t xml:space="preserve">1u X7R</t>
   </si>
   <si>
+    <t xml:space="preserve">Global Electronica (agregar: CM105 MLCC THD 1uF 50V X7R)</t>
+  </si>
+  <si>
     <t xml:space="preserve">cond. poliester (film)</t>
   </si>
   <si>
@@ -184,9 +187,15 @@
     <t xml:space="preserve">cond. poliester o C0G</t>
   </si>
   <si>
+    <t xml:space="preserve">Global Electronica (agregar: 2A104K poliester 100nF 100V + 2A473J poliester 47nF 100V, en paralelo (par))</t>
+  </si>
+  <si>
     <t xml:space="preserve">15n</t>
   </si>
   <si>
+    <t xml:space="preserve">Global Electronica (agregar: 2A153J poliester 15nF 100V)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.2n</t>
   </si>
   <si>
@@ -241,13 +250,10 @@
     <t xml:space="preserve">Avisos de la compra</t>
   </si>
   <si>
-    <t xml:space="preserve">FALTAN en los carritos: Cm1 150 nF x4 (MFB) y C21 15 nF x4 (LPF Sallen-Key). Sin ellos el canal no funciona.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALTAN: 1 uF ceramico X7R x2 para la salida del LDO; electrodos, cables de electrodo, jumpers Dupont (tira M-H y tira M-M), perfboard, tiras de header 1x40 y alcohol.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERIFICAR el microfono: el carrito dice INMP411; el diseno usa el INMP441 (I2S).</t>
+    <t xml:space="preserve">AGREGAR al carrito de Global: 4 x 2A104K (100n poliester) + 4 x 2A473J (47n poliester) para Cm1 (100n + 47n en paralelo = 147 nF); 4 x 2A153J (15n poliester) para C21; 2 x CM105 (1 uF MLCC X7R) para la salida del LDO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendiente (otra tienda): electrodos, cables de electrodo, jumpers Dupont (tira M-H y tira M-M), perfboard, tiras de header 1x40 y alcohol.</t>
   </si>
   <si>
     <t xml:space="preserve">Resistencias de carbon 5 % en vez de pelicula metalica 1 %: aceptado para la demo (ganancia por canal +-7 %, se normaliza en firmware). Para produccion: 1 %.</t>
@@ -715,7 +721,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1313,7 +1319,9 @@
       <c r="C26" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="5"/>
+      <c r="D26" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E26" s="5"/>
       <c r="F26" s="6"/>
       <c r="G26" s="7" t="str">
@@ -1332,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>12</v>
@@ -1353,15 +1361,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="5"/>
+        <v>54</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="E28" s="5"/>
       <c r="F28" s="6"/>
       <c r="G28" s="7" t="str">
@@ -1374,15 +1384,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="5"/>
+        <v>54</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="E29" s="5"/>
       <c r="F29" s="6"/>
       <c r="G29" s="7" t="str">
@@ -1395,13 +1407,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>12</v>
@@ -1422,13 +1434,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>16</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>12</v>
@@ -1449,13 +1461,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>12</v>
@@ -1476,13 +1488,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>12</v>
@@ -1503,13 +1515,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>12</v>
@@ -1530,13 +1542,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>12</v>
@@ -1557,13 +1569,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>31</v>
@@ -1584,13 +1596,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>12</v>
@@ -1611,13 +1623,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>12</v>
@@ -1638,13 +1650,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>12</v>
@@ -1665,13 +1677,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>12</v>
@@ -1692,13 +1704,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B41" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>12</v>
@@ -1719,13 +1731,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B42" s="4" t="n">
         <v>12</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>12</v>
@@ -1746,13 +1758,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>12</v>
@@ -1773,7 +1785,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F44" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G44" s="11" t="n">
         <f aca="false">SUM(G4:G43)</f>
@@ -1782,37 +1794,32 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
+++ b/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="134">
   <si>
     <t xml:space="preserve">BoM compacta AFE sEMG AuraVox (3 canales, incluye repuesto). Detalle por modulo en BoM_AFE_AuraVox.xlsx</t>
   </si>
@@ -142,10 +142,16 @@
     <t xml:space="preserve">Regulador LDO 3.3 V TLV75733PDBVR (Global 014-75733)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tira de headers 1x40 2.54 THT (1 macho + 1 hembra)</t>
+    <t xml:space="preserve">hembra 1x40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tira de header hembra 1x40 2.54 THT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">macho 1x40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tira de header macho 1x40 2.54 THT</t>
   </si>
   <si>
     <t xml:space="preserve">100p</t>
@@ -175,9 +181,6 @@
     <t xml:space="preserve">1u X7R</t>
   </si>
   <si>
-    <t xml:space="preserve">Global Electronica (agregar: CM105 MLCC THD 1uF 50V X7R)</t>
-  </si>
-  <si>
     <t xml:space="preserve">cond. poliester (film)</t>
   </si>
   <si>
@@ -187,13 +190,10 @@
     <t xml:space="preserve">cond. poliester o C0G</t>
   </si>
   <si>
-    <t xml:space="preserve">Global Electronica (agregar: 2A104K poliester 100nF 100V + 2A473J poliester 47nF 100V, en paralelo (par))</t>
-  </si>
-  <si>
     <t xml:space="preserve">15n</t>
   </si>
   <si>
-    <t xml:space="preserve">Global Electronica (agregar: 2A153J poliester 15nF 100V)</t>
+    <t xml:space="preserve">Global Electronica (agregar: 2A103J poliester 10nF 100V + 2A472K poliester 4.7nF 100V, en paralelo (par))</t>
   </si>
   <si>
     <t xml:space="preserve">2.2n</t>
@@ -247,10 +247,169 @@
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
+    <t xml:space="preserve">FALTA COMPRAR (no esta en los carritos del 4-oct-2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Que</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buscar como</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15n Condensador de realimentacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2A103J poliester 10nF 100V + 2A472K poliester 4.7nF 100V, en paralelo (par)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global (agregar al carrito)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 nF agotado (2A153J en Global; tampoco en MechatronicStore): 10n + 4.7n en paralelo = 14.7 nF (f0 +1 %, Q -1 %). Stock al 4-oct: 2A103J 22 u, 2A472K 122 u. Cantidad en pares; precio del par ($50 + $60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jumper Dupont M-H Cable a Arduino A1..A3 del STM32N6570-DK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cable dupont macho-hembra (tira de 40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MechatronicStore / Global. 1 tira de 40 M-H cubre las 3 filas M-H (14 cables)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CH1-A1 (PA9), CH2-A2 (PA10), CH3-A3 (PA12). Mas 1 cable de GND. A0 no: comparte ADC con USB1 ISENSE (UM3300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jumper Dupont M-H Cable 5 V y GND desde el DK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cable dupont macho-hembra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MechatronicStore / Global (misma tira M-H)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usar powerbank o PC a bateria mientras haya electrodos puestos (ver Notas de seguridad)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skintact FS-RG1/10 32x41 Electrodo Ag/AgCl con broche 4 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skintact FS-RG1/10 / Kendall Arbo H124SG 24 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiendas de insumos medicos / Mercado Libre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 por sesion (6 de senal + 1 RLD); caja de 50. Skintact para CH1, CH3 y RLD. CH2: Arbo H124SG (24 mm) o par sobre el menton. ISIMED 55x55 solo como RLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">broche 4 mm a pin Cable de electrodo con broche (snap) 4 mm, idealmente apantallado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cable electrodo snap 4 mm / cable ECG broche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MechatronicStore ("cable de electrodos AD8232") / tiendas medicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uno por electrodo; trenzar los dos de cada par. REVISAR EL TERMINAL antes de comprar: debe calzar en header hembra 2.54 mm. Si termina en DIN 1.5 mm touchproof (DIN 42802), cortar y crimpar terminal Dupont hembra o comprar bases touchproof. Alternativa: cable de 3 electrodos con jack 3.5 mm (el de los kits AD8232) + jack hembra 3.5 mm TRS en la placa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jumper Dupont M-M Bus de 8 cables Dupont macho (separado de una tira de 40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cable dupont macho-macho 20 cm tira 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MechatronicStore / Global. 1 tira de 40 M-M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lado macho al conector 2x8; el otro extremo se une a los cables de electrodo (soldado + termorretractil o enchufado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alcohol isopropilico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farmacia / ferreteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparar la piel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 x 15 cm Perfboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">placa perforada 10x15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global (tarjetas para prototipos) / MechatronicStore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jumper Dupont M-H Cables Dupont para el microfono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VDD 3.3V, GND, SCK, WS, SD, L/R (L/R a GND)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estano 0.5-0.8 mm con nucleo de flux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soldadura estano 0.8 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global (soldadura)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">insumo, no esta en el esquematico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux (lapiz o pasta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global (flux y mallas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imprescindible para soldar los TS922 en los S08D8 (insumo, no esta en el esquematico)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malla desoldadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malla desoldadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para sacar los trimmers de los modulos INA333 (insumo, no esta en el esquematico)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termorretractil 2-3 mm (surtido)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tubo termo retractil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uniones bus Dupont - cable de electrodo (insumo, no esta en el esquematico)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Avisos de la compra</t>
   </si>
   <si>
-    <t xml:space="preserve">AGREGAR al carrito de Global: 4 x 2A104K (100n poliester) + 4 x 2A473J (47n poliester) para Cm1 (100n + 47n en paralelo = 147 nF); 4 x 2A153J (15n poliester) para C21; 2 x CM105 (1 uF MLCC X7R) para la salida del LDO.</t>
+    <t xml:space="preserve">AGREGAR al carrito de Global: 4 x 2A103J (10n poliester) + 4 x 2A472K (4.7n poliester) para C21 (10n + 4.7n en paralelo = 14.7 nF; el 15 nF esta agotado).</t>
   </si>
   <si>
     <t xml:space="preserve">Pendiente (otra tienda): electrodos, cables de electrodo, jumpers Dupont (tira M-H y tira M-M), perfboard, tiras de header 1x40 y alcohol.</t>
@@ -273,7 +432,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,6 +501,14 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -416,7 +583,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -463,6 +630,14 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -721,7 +896,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1131,20 +1306,26 @@
         <v>40</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="7" t="str">
+      <c r="D19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="G19" s="7" t="n">
         <f aca="false">IF(OR(E19="",F19=""),"",E19*F19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>14</v>
+        <v>490</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1152,7 +1333,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>43</v>
@@ -1161,14 +1342,14 @@
         <v>12</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>40</v>
+        <v>490</v>
       </c>
       <c r="G20" s="7" t="n">
         <f aca="false">IF(OR(E20="",F20=""),"",E20*F20)</f>
-        <v>160</v>
+        <v>490</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>6</v>
@@ -1179,23 +1360,23 @@
         <v>44</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G21" s="7" t="n">
         <f aca="false">IF(OR(E21="",F21=""),"",E21*F21)</f>
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>6</v>
@@ -1203,26 +1384,26 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="D22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G22" s="7" t="n">
         <f aca="false">IF(OR(E22="",F22=""),"",E22*F22)</f>
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>6</v>
@@ -1230,26 +1411,26 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G23" s="7" t="n">
         <f aca="false">IF(OR(E23="",F23=""),"",E23*F23)</f>
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>6</v>
@@ -1260,23 +1441,23 @@
         <v>48</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G24" s="7" t="n">
         <f aca="false">IF(OR(E24="",F24=""),"",E24*F24)</f>
-        <v>350</v>
+        <v>480</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>6</v>
@@ -1284,26 +1465,26 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="D25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G25" s="7" t="n">
         <f aca="false">IF(OR(E25="",F25=""),"",E25*F25)</f>
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>6</v>
@@ -1311,49 +1492,53 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="7" t="str">
+        <v>12</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G26" s="7" t="n">
         <f aca="false">IF(OR(E26="",F26=""),"",E26*F26)</f>
-        <v/>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>14</v>
+        <v>270</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G27" s="7" t="n">
         <f aca="false">IF(OR(E27="",F27=""),"",E27*F27)</f>
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>6</v>
@@ -1361,99 +1546,103 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="D28" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7" t="str">
+        <v>12</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <f aca="false">IF(OR(E28="",F28=""),"",E28*F28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>14</v>
+        <v>320</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7" t="str">
+        <v>12</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="G29" s="7" t="n">
         <f aca="false">IF(OR(E29="",F29=""),"",E29*F29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>14</v>
+        <v>520</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G30" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="7" t="str">
         <f aca="false">IF(OR(E30="",F30=""),"",E30*F30)</f>
-        <v>120</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>6</v>
+        <v/>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G31" s="7" t="n">
         <f aca="false">IF(OR(E31="",F31=""),"",E31*F31)</f>
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>6</v>
@@ -1461,26 +1650,26 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G32" s="7" t="n">
         <f aca="false">IF(OR(E32="",F32=""),"",E32*F32)</f>
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>6</v>
@@ -1488,10 +1677,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B33" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>62</v>
@@ -1500,14 +1689,14 @@
         <v>12</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="G33" s="7" t="n">
         <f aca="false">IF(OR(E33="",F33=""),"",E33*F33)</f>
-        <v>1958</v>
+        <v>300</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>6</v>
@@ -1515,10 +1704,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>62</v>
@@ -1527,14 +1716,14 @@
         <v>12</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="G34" s="7" t="n">
         <f aca="false">IF(OR(E34="",F34=""),"",E34*F34)</f>
-        <v>80</v>
+        <v>1958</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>6</v>
@@ -1542,10 +1731,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B35" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>62</v>
@@ -1554,14 +1743,14 @@
         <v>12</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G35" s="7" t="n">
         <f aca="false">IF(OR(E35="",F35=""),"",E35*F35)</f>
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>6</v>
@@ -1569,26 +1758,26 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B36" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G36" s="7" t="n">
         <f aca="false">IF(OR(E36="",F36=""),"",E36*F36)</f>
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>6</v>
@@ -1596,26 +1785,26 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B37" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G37" s="7" t="n">
         <f aca="false">IF(OR(E37="",F37=""),"",E37*F37)</f>
-        <v>125</v>
+        <v>800</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>6</v>
@@ -1623,7 +1812,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>4</v>
@@ -1635,14 +1824,14 @@
         <v>12</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G38" s="7" t="n">
         <f aca="false">IF(OR(E38="",F38=""),"",E38*F38)</f>
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>6</v>
@@ -1650,10 +1839,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B39" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>62</v>
@@ -1662,14 +1851,14 @@
         <v>12</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G39" s="7" t="n">
         <f aca="false">IF(OR(E39="",F39=""),"",E39*F39)</f>
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>6</v>
@@ -1677,10 +1866,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B40" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>62</v>
@@ -1689,14 +1878,14 @@
         <v>12</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G40" s="7" t="n">
         <f aca="false">IF(OR(E40="",F40=""),"",E40*F40)</f>
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>6</v>
@@ -1704,10 +1893,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>62</v>
@@ -1716,14 +1905,14 @@
         <v>12</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G41" s="7" t="n">
         <f aca="false">IF(OR(E41="",F41=""),"",E41*F41)</f>
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>6</v>
@@ -1731,10 +1920,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B42" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>62</v>
@@ -1743,14 +1932,14 @@
         <v>12</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>25</v>
       </c>
       <c r="G42" s="7" t="n">
         <f aca="false">IF(OR(E42="",F42=""),"",E42*F42)</f>
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H42" s="8" t="s">
         <v>6</v>
@@ -1758,10 +1947,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B43" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>62</v>
@@ -1770,56 +1959,324 @@
         <v>12</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G43" s="7" t="n">
         <f aca="false">IF(OR(E43="",F43=""),"",E43*F43)</f>
+        <v>300</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <f aca="false">IF(OR(E44="",F44=""),"",E44*F44)</f>
         <v>120</v>
       </c>
-      <c r="H43" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F44" s="10" t="s">
+      <c r="H44" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F45" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G44" s="11" t="n">
-        <f aca="false">SUM(G4:G43)</f>
-        <v>65643</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10" t="s">
-        <v>75</v>
+      <c r="G45" s="11" t="n">
+        <f aca="false">SUM(G4:G44)</f>
+        <v>67243</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12" t="s">
+      <c r="B48" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="12" t="s">
+      <c r="C48" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="12" t="s">
+      <c r="D48" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12" t="s">
+      <c r="E48" s="3" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="293.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="217.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="496.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="153.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E56" s="13"/>
+    </row>
+    <row r="57" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="14" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
+++ b/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="101">
   <si>
     <t xml:space="preserve">BoM compacta AFE sEMG AuraVox (3 canales, incluye repuesto). Detalle por modulo en BoM_AFE_AuraVox.xlsx</t>
   </si>
@@ -73,6 +73,9 @@
     <t xml:space="preserve">Bus de 8 cables Dupont macho (separado de una tira de 40)</t>
   </si>
   <si>
+    <t xml:space="preserve">Por confirmar</t>
+  </si>
+  <si>
     <t xml:space="preserve">jumper Dupont M-H</t>
   </si>
   <si>
@@ -136,6 +139,12 @@
     <t xml:space="preserve">Perfboard</t>
   </si>
   <si>
+    <t xml:space="preserve">ya lo tengo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya lo tengo</t>
+  </si>
+  <si>
     <t xml:space="preserve">TLV75733PDBVR</t>
   </si>
   <si>
@@ -193,9 +202,6 @@
     <t xml:space="preserve">15n</t>
   </si>
   <si>
-    <t xml:space="preserve">Global Electronica (agregar: 2A103J poliester 10nF 100V + 2A472K poliester 4.7nF 100V, en paralelo (par))</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.2n</t>
   </si>
   <si>
@@ -265,42 +271,6 @@
     <t xml:space="preserve">Notas</t>
   </si>
   <si>
-    <t xml:space="preserve">15n Condensador de realimentacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2A103J poliester 10nF 100V + 2A472K poliester 4.7nF 100V, en paralelo (par)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global (agregar al carrito)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 nF agotado (2A153J en Global; tampoco en MechatronicStore): 10n + 4.7n en paralelo = 14.7 nF (f0 +1 %, Q -1 %). Stock al 4-oct: 2A103J 22 u, 2A472K 122 u. Cantidad en pares; precio del par ($50 + $60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jumper Dupont M-H Cable a Arduino A1..A3 del STM32N6570-DK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cable dupont macho-hembra (tira de 40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MechatronicStore / Global. 1 tira de 40 M-H cubre las 3 filas M-H (14 cables)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CH1-A1 (PA9), CH2-A2 (PA10), CH3-A3 (PA12). Mas 1 cable de GND. A0 no: comparte ADC con USB1 ISENSE (UM3300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jumper Dupont M-H Cable 5 V y GND desde el DK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cable dupont macho-hembra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MechatronicStore / Global (misma tira M-H)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usar powerbank o PC a bateria mientras haya electrodos puestos (ver Notas de seguridad)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skintact FS-RG1/10 32x41 Electrodo Ag/AgCl con broche 4 mm</t>
   </si>
   <si>
@@ -325,18 +295,6 @@
     <t xml:space="preserve">Uno por electrodo; trenzar los dos de cada par. REVISAR EL TERMINAL antes de comprar: debe calzar en header hembra 2.54 mm. Si termina en DIN 1.5 mm touchproof (DIN 42802), cortar y crimpar terminal Dupont hembra o comprar bases touchproof. Alternativa: cable de 3 electrodos con jack 3.5 mm (el de los kits AD8232) + jack hembra 3.5 mm TRS en la placa</t>
   </si>
   <si>
-    <t xml:space="preserve">jumper Dupont M-M Bus de 8 cables Dupont macho (separado de una tira de 40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cable dupont macho-macho 20 cm tira 40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MechatronicStore / Global. 1 tira de 40 M-M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lado macho al conector 2x8; el otro extremo se une a los cables de electrodo (soldado + termorretractil o enchufado)</t>
-  </si>
-  <si>
     <t xml:space="preserve">alcohol isopropilico</t>
   </si>
   <si>
@@ -346,73 +304,16 @@
     <t xml:space="preserve">Preparar la piel</t>
   </si>
   <si>
-    <t xml:space="preserve">10 x 15 cm Perfboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">placa perforada 10x15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global (tarjetas para prototipos) / MechatronicStore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jumper Dupont M-H Cables Dupont para el microfono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VDD 3.3V, GND, SCK, WS, SD, L/R (L/R a GND)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estano 0.5-0.8 mm con nucleo de flux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soldadura estano 0.8 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global (soldadura)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">insumo, no esta en el esquematico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flux (lapiz o pasta)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global (flux y mallas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imprescindible para soldar los TS922 en los S08D8 (insumo, no esta en el esquematico)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malla desoldadora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">malla desoldadora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Para sacar los trimmers de los modulos INA333 (insumo, no esta en el esquematico)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Termorretractil 2-3 mm (surtido)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tubo termo retractil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uniones bus Dupont - cable de electrodo (insumo, no esta en el esquematico)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Avisos de la compra</t>
   </si>
   <si>
-    <t xml:space="preserve">AGREGAR al carrito de Global: 4 x 2A103J (10n poliester) + 4 x 2A472K (4.7n poliester) para C21 (10n + 4.7n en paralelo = 14.7 nF; el 15 nF esta agotado).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendiente (otra tienda): electrodos, cables de electrodo, jumpers Dupont (tira M-H y tira M-M), perfboard, tiras de header 1x40 y alcohol.</t>
+    <t xml:space="preserve">Cm1 = 100n + 47n poliester en paralelo (147 nF) y C21 = 10n + 4.7n poliester en paralelo (14.7 nF): no habia 150 nF y el 15 nF estaba agotado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta: electrodos, cables de electrodo y alcohol (ver FALTA COMPRAR). Perfboard e insumos de soldadura: ya los tienes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiras Dupont M-H y M-M: llenar tienda y precio en la hoja BoM por modulo.</t>
   </si>
   <si>
     <t xml:space="preserve">Resistencias de carbon 5 % en vez de pelicula metalica 1 %: aceptado para la demo (ganancia por canal +-7 %, se normaliza en firmware). Para produccion: 1 %.</t>
@@ -896,7 +797,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1002,68 +903,80 @@
       <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="F6" s="6"/>
       <c r="G6" s="7" t="str">
         <f aca="false">IF(OR(E6="",F6=""),"",E6*F6)</f>
         <v/>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>14</v>
+      <c r="H6" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7" t="str">
         <f aca="false">IF(OR(E7="",F7=""),"",E7*F7)</f>
         <v/>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>14</v>
+      <c r="H7" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="F8" s="6"/>
       <c r="G8" s="7" t="str">
         <f aca="false">IF(OR(E8="",F8=""),"",E8*F8)</f>
         <v/>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>14</v>
+      <c r="H8" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -1078,13 +991,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>12</v>
@@ -1105,34 +1018,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7" t="str">
         <f aca="false">IF(OR(E11="",F11=""),"",E11*F11)</f>
         <v/>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>14</v>
+      <c r="H11" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>12</v>
@@ -1153,13 +1070,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>50</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1174,16 +1091,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>4</v>
@@ -1201,13 +1118,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>12</v>
@@ -1228,13 +1145,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>12</v>
@@ -1255,34 +1172,36 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="5"/>
+        <v>38</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="E17" s="5"/>
       <c r="F17" s="6"/>
       <c r="G17" s="7" t="str">
         <f aca="false">IF(OR(E17="",F17=""),"",E17*F17)</f>
         <v/>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>14</v>
+      <c r="H17" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>12</v>
@@ -1303,16 +1222,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1</v>
@@ -1330,13 +1249,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>12</v>
@@ -1357,13 +1276,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>12</v>
@@ -1384,13 +1303,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>12</v>
@@ -1411,13 +1330,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>12</v>
@@ -1438,13 +1357,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>12</v>
@@ -1465,13 +1384,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>12</v>
@@ -1492,13 +1411,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>12</v>
@@ -1519,13 +1438,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>12</v>
@@ -1546,13 +1465,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>12</v>
@@ -1573,13 +1492,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>12</v>
@@ -1600,36 +1519,40 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7" t="str">
+        <v>12</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="G30" s="7" t="n">
         <f aca="false">IF(OR(E30="",F30=""),"",E30*F30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>14</v>
+        <v>440</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>12</v>
@@ -1650,13 +1573,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>16</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>12</v>
@@ -1677,13 +1600,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>12</v>
@@ -1704,13 +1627,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>12</v>
@@ -1731,13 +1654,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>12</v>
@@ -1758,13 +1681,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>12</v>
@@ -1785,16 +1708,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>8</v>
@@ -1812,13 +1735,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>12</v>
@@ -1839,13 +1762,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>12</v>
@@ -1866,13 +1789,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>12</v>
@@ -1893,13 +1816,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B41" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>12</v>
@@ -1920,13 +1843,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B42" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>12</v>
@@ -1947,13 +1870,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>12</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>12</v>
@@ -1974,13 +1897,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B44" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>12</v>
@@ -2001,282 +1924,119 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F45" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G45" s="11" t="n">
         <f aca="false">SUM(G4:G44)</f>
-        <v>67243</v>
+        <v>67683</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="293.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="217.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="496.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="217.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C52" s="13" t="s">
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D52" s="13" t="s">
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="E52" s="13" t="s">
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="496.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B53" s="13" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C53" s="13" t="s">
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="13" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="E53" s="13" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="14" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="153.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E56" s="13"/>
-    </row>
-    <row r="57" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="14" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="14" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="14" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="14" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="14" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
+++ b/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="121">
   <si>
     <t xml:space="preserve">BoM compacta AFE sEMG AuraVox (3 canales, incluye repuesto). Detalle por modulo en BoM_AFE_AuraVox.xlsx</t>
   </si>
@@ -61,6 +61,9 @@
     <t xml:space="preserve">Global Electronica</t>
   </si>
   <si>
+    <t xml:space="preserve">Comprado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alcohol isopropilico / gel</t>
   </si>
   <si>
@@ -73,7 +76,7 @@
     <t xml:space="preserve">Bus de 8 cables Dupont macho (separado de una tira de 40)</t>
   </si>
   <si>
-    <t xml:space="preserve">Por confirmar</t>
+    <t xml:space="preserve">Parcial</t>
   </si>
   <si>
     <t xml:space="preserve">jumper Dupont M-H</t>
@@ -193,13 +196,13 @@
     <t xml:space="preserve">cond. poliester (film)</t>
   </si>
   <si>
-    <t xml:space="preserve">150n</t>
+    <t xml:space="preserve">100n + 47n en paralelo</t>
   </si>
   <si>
     <t xml:space="preserve">cond. poliester o C0G</t>
   </si>
   <si>
-    <t xml:space="preserve">15n</t>
+    <t xml:space="preserve">10n + 4.7n en paralelo</t>
   </si>
   <si>
     <t xml:space="preserve">2.2n</t>
@@ -271,6 +274,30 @@
     <t xml:space="preserve">Notas</t>
   </si>
   <si>
+    <t xml:space="preserve">jumper Dupont M-H Cable a Arduino A1..A3 del STM32N6570-DK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cable dupont macho-hembra (tira de 40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MechatronicStore / Global. 1 tira de 40 M-H cubre las 3 filas M-H (14 cables)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compraste 2 de 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jumper Dupont M-H Cable 5 V y GND desde el DK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cable dupont macho-hembra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MechatronicStore / Global (misma tira M-H)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usar powerbank o PC a bateria mientras haya electrodos puestos (ver Notas de seguridad)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Skintact FS-RG1/10 32x41 Electrodo Ag/AgCl con broche 4 mm</t>
   </si>
   <si>
@@ -295,6 +322,18 @@
     <t xml:space="preserve">Uno por electrodo; trenzar los dos de cada par. REVISAR EL TERMINAL antes de comprar: debe calzar en header hembra 2.54 mm. Si termina en DIN 1.5 mm touchproof (DIN 42802), cortar y crimpar terminal Dupont hembra o comprar bases touchproof. Alternativa: cable de 3 electrodos con jack 3.5 mm (el de los kits AD8232) + jack hembra 3.5 mm TRS en la placa</t>
   </si>
   <si>
+    <t xml:space="preserve">jumper Dupont M-M Bus de 8 cables Dupont macho (separado de una tira de 40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cable dupont macho-macho 20 cm tira 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MechatronicStore / Global. 1 tira de 40 M-M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compraste 2 de 8</t>
+  </si>
+  <si>
     <t xml:space="preserve">alcohol isopropilico</t>
   </si>
   <si>
@@ -304,25 +343,46 @@
     <t xml:space="preserve">Preparar la piel</t>
   </si>
   <si>
+    <t xml:space="preserve">jumper Dupont M-H Cables Dupont para el microfono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VDD 3.3V, GND, SCK, WS, SD, L/R (L/R a GND)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMADO: condensadores en paralelo y polaridades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cm1 (MFB, x3 canales) = 100 nF (2A104K) EN PARALELO con 47 nF (2A473J): los dos entre el nodo MA (union Rm1-Rm2-Rm3) y GND.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21 (Sallen-Key, x3 canales) = 10 nF (2A103J) EN PARALELO con 4.7 nF (2A472K): los dos entre la union Rlb1-Rlb2 y la salida del op-amp del SK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cm0 (10 uF electrolitico): entre sus patas hay ~0 V DC; cualquier orientacion sirve. Por convencion: + hacia la salida del HPF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDO: CM105 (1 uF ceramico) en paralelo con el CE50102 (1 uF electrolitico) a la salida, pegados a los pines OUT y GND.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La simulacion ya usa los valores armados: CM1 = 147n y C21 = 14.7n.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Avisos de la compra</t>
   </si>
   <si>
-    <t xml:space="preserve">Cm1 = 100n + 47n poliester en paralelo (147 nF) y C21 = 10n + 4.7n poliester en paralelo (14.7 nF): no habia 150 nF y el 15 nF estaba agotado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Falta: electrodos, cables de electrodo y alcohol (ver FALTA COMPRAR). Perfboard e insumos de soldadura: ya los tienes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiras Dupont M-H y M-M: llenar tienda y precio en la hoja BoM por modulo.</t>
+    <t xml:space="preserve">Pedidos hechos el 4-oct-2026: Global $39.433 (retiro en tienda) + MechatronicStore $28.450 (Bluexpress) = $67.883.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dupont: JPMH20/JPMM20 son cables SUELTOS. Tienes 2 M-H y 2 M-M; el diseno usa 14 M-H y 8 M-M (faltan 12 M-H y 6 M-M; Global tiene stock, $50 c/u).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta: electrodos, cables de electrodo y alcohol (ver FALTA COMPRAR).</t>
   </si>
   <si>
     <t xml:space="preserve">Resistencias de carbon 5 % en vez de pelicula metalica 1 %: aceptado para la demo (ganancia por canal +-7 %, se normaliza en firmware). Para produccion: 1 %.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ajustes opcionales: S08D8 12 -&gt; 7 (ahorro $1.250); 100k 2 W -&gt; 1/4 W si hay stock (ahorro ~$1.700).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precios con IVA, sin despacho.</t>
+    <t xml:space="preserve">Precios con IVA.</t>
   </si>
 </sst>
 </file>
@@ -333,7 +393,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,6 +474,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3A5F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -484,7 +552,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -539,6 +607,10 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -797,7 +869,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -869,18 +941,18 @@
         <v>3000</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -890,93 +962,93 @@
         <v/>
       </c>
       <c r="H5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="7" t="str">
+        <v>2</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <f aca="false">IF(OR(E6="",F6=""),"",E6*F6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>6</v>
+        <v>100</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="6"/>
       <c r="G7" s="7" t="str">
         <f aca="false">IF(OR(E7="",F7=""),"",E7*F7)</f>
         <v/>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>6</v>
+      <c r="H7" s="9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="7" t="str">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <f aca="false">IF(OR(E8="",F8=""),"",E8*F8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>6</v>
+        <v>100</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -986,18 +1058,18 @@
         <v/>
       </c>
       <c r="H9" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>12</v>
@@ -1013,43 +1085,39 @@
         <v>900</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>6</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
       <c r="F11" s="6"/>
       <c r="G11" s="7" t="str">
         <f aca="false">IF(OR(E11="",F11=""),"",E11*F11)</f>
         <v/>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>6</v>
+      <c r="H11" s="9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>12</v>
@@ -1065,18 +1133,18 @@
         <v>300</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>50</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1086,21 +1154,21 @@
         <v/>
       </c>
       <c r="H13" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>4</v>
@@ -1113,18 +1181,18 @@
         <v>27160</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>12</v>
@@ -1140,18 +1208,18 @@
         <v>7790</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>12</v>
@@ -1167,21 +1235,21 @@
         <v>17340</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="6"/>
@@ -1190,18 +1258,18 @@
         <v/>
       </c>
       <c r="H17" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>12</v>
@@ -1217,21 +1285,21 @@
         <v>1900</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1</v>
@@ -1244,18 +1312,18 @@
         <v>490</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>12</v>
@@ -1271,18 +1339,18 @@
         <v>490</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>12</v>
@@ -1298,18 +1366,18 @@
         <v>160</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>12</v>
@@ -1325,18 +1393,18 @@
         <v>600</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>12</v>
@@ -1352,18 +1420,18 @@
         <v>240</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>12</v>
@@ -1379,18 +1447,18 @@
         <v>480</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>12</v>
@@ -1406,18 +1474,18 @@
         <v>350</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>12</v>
@@ -1433,18 +1501,18 @@
         <v>270</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>12</v>
@@ -1460,18 +1528,18 @@
         <v>100</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>12</v>
@@ -1487,18 +1555,18 @@
         <v>320</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>12</v>
@@ -1514,18 +1582,18 @@
         <v>520</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>12</v>
@@ -1541,18 +1609,18 @@
         <v>440</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>12</v>
@@ -1568,18 +1636,18 @@
         <v>120</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>16</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>12</v>
@@ -1595,18 +1663,18 @@
         <v>320</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>12</v>
@@ -1622,18 +1690,18 @@
         <v>300</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>12</v>
@@ -1649,18 +1717,18 @@
         <v>1958</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>12</v>
@@ -1676,18 +1744,18 @@
         <v>80</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>12</v>
@@ -1703,21 +1771,21 @@
         <v>120</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>8</v>
@@ -1730,18 +1798,18 @@
         <v>800</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>12</v>
@@ -1757,18 +1825,18 @@
         <v>125</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>12</v>
@@ -1784,18 +1852,18 @@
         <v>120</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>12</v>
@@ -1811,18 +1879,18 @@
         <v>250</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B41" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>12</v>
@@ -1838,18 +1906,18 @@
         <v>120</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B42" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>12</v>
@@ -1865,18 +1933,18 @@
         <v>100</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>12</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>12</v>
@@ -1892,18 +1960,18 @@
         <v>300</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B44" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>12</v>
@@ -1919,124 +1987,217 @@
         <v>120</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F45" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G45" s="11" t="n">
         <f aca="false">SUM(G4:G44)</f>
-        <v>67683</v>
+        <v>67883</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="217.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="217.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="B49" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="496.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="n">
+      <c r="B51" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="496.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B50" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D50" s="13" t="s">
+      <c r="B52" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E50" s="13" t="s">
+      <c r="D55" s="13" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="14" t="s">
-        <v>97</v>
+      <c r="E55" s="13" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="14" t="s">
-        <v>99</v>
+      <c r="A58" s="15" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="14" t="s">
-        <v>100</v>
+      <c r="A59" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="15" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
+++ b/docs/afe-emg/BoM_AFE_AuraVox_compacta.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="120">
   <si>
     <t xml:space="preserve">BoM compacta AFE sEMG AuraVox (3 canales, incluye repuesto). Detalle por modulo en BoM_AFE_AuraVox.xlsx</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bus de 8 cables Dupont macho (separado de una tira de 40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial</t>
   </si>
   <si>
     <t xml:space="preserve">jumper Dupont M-H</t>
@@ -552,68 +549,72 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -872,1332 +873,1332 @@
   <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="D4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="7" t="n">
         <v>250</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <f aca="false">IF(OR(E4="",F4=""),"",E4*F4)</f>
         <v>3000</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7" t="str">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8" t="str">
         <f aca="false">IF(OR(E5="",F5=""),"",E5*F5)</f>
         <v/>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="F6" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <f aca="false">IF(OR(E6="",F6=""),"",E6*F6)</f>
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="H6" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="7" t="str">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8" t="str">
         <f aca="false">IF(OR(E7="",F7=""),"",E7*F7)</f>
         <v/>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="4" t="n">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <f aca="false">IF(OR(E8="",F8=""),"",E8*F8)</f>
+        <v>2100</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <f aca="false">IF(OR(E8="",F8=""),"",E8*F8)</f>
-        <v>100</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="7" t="str">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8" t="str">
         <f aca="false">IF(OR(E9="",F9=""),"",E9*F9)</f>
         <v/>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="5" t="n">
+      <c r="D10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <f aca="false">IF(OR(E10="",F10=""),"",E10*F10)</f>
         <v>900</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="4" t="n">
+      <c r="A11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="7" t="str">
+      <c r="C11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8" t="str">
         <f aca="false">IF(OR(E11="",F11=""),"",E11*F11)</f>
         <v/>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="D12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="8" t="n">
         <f aca="false">IF(OR(E12="",F12=""),"",E12*F12)</f>
         <v>300</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="7" t="str">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8" t="str">
         <f aca="false">IF(OR(E13="",F13=""),"",E13*F13)</f>
         <v/>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="D14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>6790</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="8" t="n">
         <f aca="false">IF(OR(E14="",F14=""),"",E14*F14)</f>
         <v>27160</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="D15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>7790</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="8" t="n">
         <f aca="false">IF(OR(E15="",F15=""),"",E15*F15)</f>
         <v>7790</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="D16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>2890</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="8" t="n">
         <f aca="false">IF(OR(E16="",F16=""),"",E16*F16)</f>
         <v>17340</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="7" t="str">
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="8" t="str">
         <f aca="false">IF(OR(E17="",F17=""),"",E17*F17)</f>
         <v/>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="B18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="D18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="8" t="n">
         <f aca="false">IF(OR(E18="",F18=""),"",E18*F18)</f>
         <v>1900</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="D19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>490</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="8" t="n">
         <f aca="false">IF(OR(E19="",F19=""),"",E19*F19)</f>
         <v>490</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="D20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>490</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="8" t="n">
         <f aca="false">IF(OR(E20="",F20=""),"",E20*F20)</f>
         <v>490</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="D21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="8" t="n">
         <f aca="false">IF(OR(E21="",F21=""),"",E21*F21)</f>
         <v>160</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="4" t="n">
+      <c r="A22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="5" t="n">
+      <c r="C22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="8" t="n">
         <f aca="false">IF(OR(E22="",F22=""),"",E22*F22)</f>
         <v>600</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="4" t="n">
+      <c r="A23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="5" t="n">
+      <c r="C23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="8" t="n">
         <f aca="false">IF(OR(E23="",F23=""),"",E23*F23)</f>
         <v>240</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F24" s="6" t="n">
+      <c r="D24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="8" t="n">
         <f aca="false">IF(OR(E24="",F24=""),"",E24*F24)</f>
         <v>480</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="4" t="n">
+      <c r="A25" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="5" t="n">
+      <c r="C25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="8" t="n">
         <f aca="false">IF(OR(E25="",F25=""),"",E25*F25)</f>
         <v>350</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="4" t="n">
+      <c r="A26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="5" t="n">
+      <c r="C26" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="8" t="n">
         <f aca="false">IF(OR(E26="",F26=""),"",E26*F26)</f>
         <v>270</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="4" t="n">
+      <c r="A27" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="5" t="n">
+      <c r="C27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="8" t="n">
         <f aca="false">IF(OR(E27="",F27=""),"",E27*F27)</f>
         <v>100</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="4" t="n">
+      <c r="A28" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="5" t="n">
+      <c r="C28" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="8" t="n">
         <f aca="false">IF(OR(E28="",F28=""),"",E28*F28)</f>
         <v>320</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="D29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="8" t="n">
         <f aca="false">IF(OR(E29="",F29=""),"",E29*F29)</f>
         <v>520</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="4" t="n">
+      <c r="A30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="5" t="n">
+      <c r="C30" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="8" t="n">
         <f aca="false">IF(OR(E30="",F30=""),"",E30*F30)</f>
         <v>440</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="4" t="n">
+      <c r="A31" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" s="5" t="n">
+      <c r="C31" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="8" t="n">
         <f aca="false">IF(OR(E31="",F31=""),"",E31*F31)</f>
         <v>120</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="D32" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="8" t="n">
         <f aca="false">IF(OR(E32="",F32=""),"",E32*F32)</f>
         <v>320</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="5" t="n">
+      <c r="D33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="8" t="n">
         <f aca="false">IF(OR(E33="",F33=""),"",E33*F33)</f>
         <v>300</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="4" t="n">
+      <c r="A34" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="5" t="n">
+      <c r="C34" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="7" t="n">
         <v>178</v>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="8" t="n">
         <f aca="false">IF(OR(E34="",F34=""),"",E34*F34)</f>
         <v>1958</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" s="4" t="n">
+      <c r="A35" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="5" t="n">
+      <c r="C35" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="8" t="n">
         <f aca="false">IF(OR(E35="",F35=""),"",E35*F35)</f>
         <v>80</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" s="4" t="n">
+      <c r="A36" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="5" t="n">
+      <c r="C36" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="8" t="n">
         <f aca="false">IF(OR(E36="",F36=""),"",E36*F36)</f>
         <v>120</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B37" s="4" t="n">
+      <c r="A37" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="5" t="n">
+      <c r="C37" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="8" t="n">
         <f aca="false">IF(OR(E37="",F37=""),"",E37*F37)</f>
         <v>800</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" s="4" t="n">
+      <c r="A38" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="5" t="n">
+      <c r="C38" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="8" t="n">
         <f aca="false">IF(OR(E38="",F38=""),"",E38*F38)</f>
         <v>125</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" s="4" t="n">
+      <c r="A39" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="5" t="n">
+      <c r="C39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="8" t="n">
         <f aca="false">IF(OR(E39="",F39=""),"",E39*F39)</f>
         <v>120</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B40" s="4" t="n">
+      <c r="A40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="5" t="n">
+      <c r="C40" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="8" t="n">
         <f aca="false">IF(OR(E40="",F40=""),"",E40*F40)</f>
         <v>250</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B41" s="4" t="n">
+      <c r="A41" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="5" t="n">
+      <c r="C41" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="8" t="n">
         <f aca="false">IF(OR(E41="",F41=""),"",E41*F41)</f>
         <v>120</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B42" s="4" t="n">
+      <c r="A42" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="5" t="n">
+      <c r="C42" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="G42" s="8" t="n">
         <f aca="false">IF(OR(E42="",F42=""),"",E42*F42)</f>
         <v>100</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F43" s="6" t="n">
+      <c r="A43" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F43" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="G43" s="8" t="n">
         <f aca="false">IF(OR(E43="",F43=""),"",E43*F43)</f>
         <v>300</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B44" s="4" t="n">
+      <c r="A44" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="5" t="n">
+      <c r="C44" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="8" t="n">
         <f aca="false">IF(OR(E44="",F44=""),"",E44*F44)</f>
         <v>120</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <f aca="false">SUM(G4:G44)</f>
+        <v>71883</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G45" s="11" t="n">
-        <f aca="false">SUM(G4:G44)</f>
-        <v>67883</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
+      <c r="B48" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="E48" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E48" s="3" t="s">
+    </row>
+    <row r="49" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" s="14" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="n">
+      <c r="C49" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B49" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E49" s="13" t="s">
+      <c r="B50" s="14" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B50" s="13" t="s">
+      <c r="C50" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="D50" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="E50" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E50" s="13" t="s">
+    </row>
+    <row r="51" customFormat="false" ht="217.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="14" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="217.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13" t="s">
+      <c r="C51" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="D51" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="E51" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E51" s="13" t="s">
+    </row>
+    <row r="52" customFormat="false" ht="496.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B52" s="14" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="496.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B52" s="13" t="s">
+      <c r="C52" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="D52" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="E52" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E52" s="13" t="s">
+    </row>
+    <row r="53" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B53" s="14" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="n">
+      <c r="C53" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B53" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E54" s="13" t="s">
+      <c r="B55" s="14" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B55" s="13" t="s">
+      <c r="C55" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E55" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C55" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E55" s="13" t="s">
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="14" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="16" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="15" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15" t="s">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="16" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="15" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="16" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="15" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="11" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="10" t="s">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="16" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="15" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="15" t="s">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="16" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="16" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="15" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="16" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="15" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
